--- a/Result/profitability/6761.xlsx
+++ b/Result/profitability/6761.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM30"/>
+  <dimension ref="A1:AM31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4240,6 +4240,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>6761</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>526</v>
+      </c>
+      <c r="D31" t="n">
+        <v>326</v>
+      </c>
+      <c r="E31" t="n">
+        <v>200</v>
+      </c>
+      <c r="F31" t="n">
+        <v>38.06</v>
+      </c>
+      <c r="G31" t="n">
+        <v>83</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>15.75%</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>82</v>
+      </c>
+      <c r="K31" t="n">
+        <v>70</v>
+      </c>
+      <c r="L31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.8475</v>
+      </c>
+      <c r="N31" t="n">
+        <v>36.06875</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
+      </c>
+      <c r="V31" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.4199999999999999</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.2625</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>-0.2399999999999949</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-0.006266318537858862</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.3466666666666667</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.730000000000004</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.1086513253713954</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK31" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
